--- a/WTSP spectrogram usability.xlsx
+++ b/WTSP spectrogram usability.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="3321" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B702392-BE2A-47F2-B7E9-037C05941BB9}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mcentee_lab_2/Documents/GitHub/White-throated-sparrow/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377AC328-72A3-CA4C-9BBA-EA88F4E54A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="22460" windowHeight="15140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1293,9 +1298,6 @@
     <t>XC265364_terminal_strophes.wav</t>
   </si>
   <si>
-    <t>XC284004_terminal_strophes.wav</t>
-  </si>
-  <si>
     <t>XC296901_terminal_strophes.wav</t>
   </si>
   <si>
@@ -1399,13 +1401,16 @@
   </si>
   <si>
     <t>XC480251_terminal_strophes.wav</t>
+  </si>
+  <si>
+    <t>XC248004_terminal_strophes.wav</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1803,18 +1808,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I413"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1843,7 +1848,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1854,7 +1859,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1868,7 +1873,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1879,7 +1884,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1893,7 +1898,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1904,7 +1909,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1915,7 +1920,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1926,7 +1931,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -1937,7 +1942,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1951,7 +1956,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -1962,7 +1967,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1976,7 +1981,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -1987,7 +1992,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -2001,7 +2006,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -2018,7 +2023,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -2029,7 +2034,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -2040,7 +2045,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -2054,7 +2059,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -2068,7 +2073,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -2079,7 +2084,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -2096,7 +2101,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -2110,7 +2115,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>35</v>
       </c>
@@ -2121,7 +2126,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -2138,7 +2143,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -2149,7 +2154,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>38</v>
       </c>
@@ -2163,7 +2168,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -2174,7 +2179,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -2185,7 +2190,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>41</v>
       </c>
@@ -2196,7 +2201,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>42</v>
       </c>
@@ -2207,7 +2212,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>43</v>
       </c>
@@ -2218,7 +2223,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>44</v>
       </c>
@@ -2229,7 +2234,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>45</v>
       </c>
@@ -2240,7 +2245,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>46</v>
       </c>
@@ -2254,7 +2259,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>47</v>
       </c>
@@ -2265,7 +2270,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>48</v>
       </c>
@@ -2288,7 +2293,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>52</v>
       </c>
@@ -2299,7 +2304,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>53</v>
       </c>
@@ -2310,7 +2315,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>54</v>
       </c>
@@ -2324,7 +2329,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>55</v>
       </c>
@@ -2338,7 +2343,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>56</v>
       </c>
@@ -2349,7 +2354,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>57</v>
       </c>
@@ -2360,7 +2365,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>58</v>
       </c>
@@ -2377,7 +2382,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>59</v>
       </c>
@@ -2388,7 +2393,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>60</v>
       </c>
@@ -2399,7 +2404,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>61</v>
       </c>
@@ -2410,7 +2415,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>62</v>
       </c>
@@ -2424,7 +2429,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>63</v>
       </c>
@@ -2435,7 +2440,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>64</v>
       </c>
@@ -2446,7 +2451,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>65</v>
       </c>
@@ -2457,7 +2462,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>66</v>
       </c>
@@ -2468,7 +2473,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>67</v>
       </c>
@@ -2479,7 +2484,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>68</v>
       </c>
@@ -2493,7 +2498,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>69</v>
       </c>
@@ -2504,7 +2509,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>70</v>
       </c>
@@ -2515,7 +2520,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>71</v>
       </c>
@@ -2526,7 +2531,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>72</v>
       </c>
@@ -2537,7 +2542,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>73</v>
       </c>
@@ -2548,7 +2553,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>74</v>
       </c>
@@ -2559,7 +2564,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>75</v>
       </c>
@@ -2573,7 +2578,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>76</v>
       </c>
@@ -2584,7 +2589,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>77</v>
       </c>
@@ -2601,7 +2606,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>78</v>
       </c>
@@ -2615,7 +2620,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>79</v>
       </c>
@@ -2629,7 +2634,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>80</v>
       </c>
@@ -2640,7 +2645,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>81</v>
       </c>
@@ -2651,7 +2656,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>82</v>
       </c>
@@ -2665,7 +2670,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>83</v>
       </c>
@@ -2676,7 +2681,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>84</v>
       </c>
@@ -2687,7 +2692,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>85</v>
       </c>
@@ -2698,7 +2703,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>86</v>
       </c>
@@ -2709,7 +2714,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>87</v>
       </c>
@@ -2720,7 +2725,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>88</v>
       </c>
@@ -2731,7 +2736,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>89</v>
       </c>
@@ -2742,7 +2747,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>90</v>
       </c>
@@ -2753,7 +2758,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>91</v>
       </c>
@@ -2764,7 +2769,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>92</v>
       </c>
@@ -2778,7 +2783,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>93</v>
       </c>
@@ -2792,7 +2797,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>94</v>
       </c>
@@ -2806,7 +2811,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>95</v>
       </c>
@@ -2817,7 +2822,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>96</v>
       </c>
@@ -2828,7 +2833,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>97</v>
       </c>
@@ -2839,7 +2844,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>98</v>
       </c>
@@ -2850,7 +2855,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>99</v>
       </c>
@@ -2861,7 +2866,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>100</v>
       </c>
@@ -2872,7 +2877,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>101</v>
       </c>
@@ -2883,7 +2888,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>102</v>
       </c>
@@ -2894,7 +2899,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>103</v>
       </c>
@@ -2905,7 +2910,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>104</v>
       </c>
@@ -2919,7 +2924,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>105</v>
       </c>
@@ -2933,7 +2938,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>106</v>
       </c>
@@ -2950,7 +2955,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>108</v>
       </c>
@@ -2970,7 +2975,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>110</v>
       </c>
@@ -2993,7 +2998,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>112</v>
       </c>
@@ -3007,7 +3012,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>113</v>
       </c>
@@ -3024,7 +3029,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>114</v>
       </c>
@@ -3041,7 +3046,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>115</v>
       </c>
@@ -3058,7 +3063,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>116</v>
       </c>
@@ -3081,7 +3086,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>120</v>
       </c>
@@ -3092,7 +3097,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>121</v>
       </c>
@@ -3109,7 +3114,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>122</v>
       </c>
@@ -3126,7 +3131,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>123</v>
       </c>
@@ -3143,7 +3148,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>124</v>
       </c>
@@ -3157,7 +3162,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>125</v>
       </c>
@@ -3171,7 +3176,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>126</v>
       </c>
@@ -3185,7 +3190,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>127</v>
       </c>
@@ -3196,7 +3201,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>128</v>
       </c>
@@ -3207,7 +3212,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>129</v>
       </c>
@@ -3221,7 +3226,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>130</v>
       </c>
@@ -3235,7 +3240,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>131</v>
       </c>
@@ -3252,7 +3257,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>132</v>
       </c>
@@ -3269,7 +3274,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>133</v>
       </c>
@@ -3286,7 +3291,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>134</v>
       </c>
@@ -3297,7 +3302,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>135</v>
       </c>
@@ -3314,7 +3319,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>136</v>
       </c>
@@ -3331,7 +3336,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>137</v>
       </c>
@@ -3348,7 +3353,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>138</v>
       </c>
@@ -3365,7 +3370,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>139</v>
       </c>
@@ -3382,7 +3387,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>140</v>
       </c>
@@ -3396,7 +3401,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>141</v>
       </c>
@@ -3410,7 +3415,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>142</v>
       </c>
@@ -3424,7 +3429,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>143</v>
       </c>
@@ -3441,7 +3446,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>144</v>
       </c>
@@ -3458,7 +3463,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>145</v>
       </c>
@@ -3475,7 +3480,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>146</v>
       </c>
@@ -3489,7 +3494,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>147</v>
       </c>
@@ -3503,7 +3508,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>148</v>
       </c>
@@ -3520,7 +3525,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>149</v>
       </c>
@@ -3531,7 +3536,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="129" spans="1:9">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>150</v>
       </c>
@@ -3548,7 +3553,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>151</v>
       </c>
@@ -3562,7 +3567,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="131" spans="1:9">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>152</v>
       </c>
@@ -3579,7 +3584,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="132" spans="1:9">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>153</v>
       </c>
@@ -3596,7 +3601,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="133" spans="1:9">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>154</v>
       </c>
@@ -3616,7 +3621,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="134" spans="1:9">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>156</v>
       </c>
@@ -3630,7 +3635,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="135" spans="1:9">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>157</v>
       </c>
@@ -3650,7 +3655,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="136" spans="1:9">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>158</v>
       </c>
@@ -3664,7 +3669,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>159</v>
       </c>
@@ -3678,7 +3683,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>160</v>
       </c>
@@ -3692,7 +3697,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="1:9">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>161</v>
       </c>
@@ -3709,7 +3714,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="140" spans="1:9">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>162</v>
       </c>
@@ -3723,7 +3728,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="141" spans="1:9">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>163</v>
       </c>
@@ -3740,7 +3745,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="142" spans="1:9">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>164</v>
       </c>
@@ -3757,7 +3762,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="143" spans="1:9">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>165</v>
       </c>
@@ -3771,7 +3776,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="144" spans="1:9">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>166</v>
       </c>
@@ -3794,7 +3799,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="145" spans="1:9">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>168</v>
       </c>
@@ -3808,7 +3813,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="146" spans="1:9">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>169</v>
       </c>
@@ -3822,7 +3827,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="147" spans="1:9">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>170</v>
       </c>
@@ -3836,7 +3841,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="148" spans="1:9">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>171</v>
       </c>
@@ -3856,7 +3861,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="149" spans="1:9">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>173</v>
       </c>
@@ -3873,7 +3878,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="150" spans="1:9">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>174</v>
       </c>
@@ -3884,7 +3889,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="151" spans="1:9">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>175</v>
       </c>
@@ -3904,7 +3909,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="152" spans="1:9">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>176</v>
       </c>
@@ -3921,7 +3926,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>177</v>
       </c>
@@ -3935,7 +3940,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="154" spans="1:9">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>178</v>
       </c>
@@ -3949,7 +3954,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="155" spans="1:9">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>179</v>
       </c>
@@ -3966,7 +3971,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="156" spans="1:9">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>180</v>
       </c>
@@ -3980,7 +3985,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="157" spans="1:9">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>181</v>
       </c>
@@ -3991,7 +3996,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:9">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>182</v>
       </c>
@@ -4008,7 +4013,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="159" spans="1:9">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>183</v>
       </c>
@@ -4022,7 +4027,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>184</v>
       </c>
@@ -4033,7 +4038,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="161" spans="1:9">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>185</v>
       </c>
@@ -4047,7 +4052,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="162" spans="1:9">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>186</v>
       </c>
@@ -4061,7 +4066,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="163" spans="1:9">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>187</v>
       </c>
@@ -4078,7 +4083,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="164" spans="1:9">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>188</v>
       </c>
@@ -4098,7 +4103,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="165" spans="1:9">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>189</v>
       </c>
@@ -4112,7 +4117,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="166" spans="1:9">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>190</v>
       </c>
@@ -4129,7 +4134,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="167" spans="1:9">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>191</v>
       </c>
@@ -4152,7 +4157,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="168" spans="1:9">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>193</v>
       </c>
@@ -4169,7 +4174,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="169" spans="1:9">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>194</v>
       </c>
@@ -4192,7 +4197,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="170" spans="1:9">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>196</v>
       </c>
@@ -4203,7 +4208,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="171" spans="1:9">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>197</v>
       </c>
@@ -4220,7 +4225,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="172" spans="1:9">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>199</v>
       </c>
@@ -4231,7 +4236,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="173" spans="1:9">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>200</v>
       </c>
@@ -4242,7 +4247,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="174" spans="1:9">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>201</v>
       </c>
@@ -4253,7 +4258,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="175" spans="1:9">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>202</v>
       </c>
@@ -4270,7 +4275,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="176" spans="1:9">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>203</v>
       </c>
@@ -4284,7 +4289,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="177" spans="1:9">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>204</v>
       </c>
@@ -4301,7 +4306,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="178" spans="1:9">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>205</v>
       </c>
@@ -4318,7 +4323,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="179" spans="1:9">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>206</v>
       </c>
@@ -4332,7 +4337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="180" spans="1:9">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>207</v>
       </c>
@@ -4346,7 +4351,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="181" spans="1:9">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>208</v>
       </c>
@@ -4360,7 +4365,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="182" spans="1:9">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>209</v>
       </c>
@@ -4380,7 +4385,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="183" spans="1:9">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>210</v>
       </c>
@@ -4394,7 +4399,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="184" spans="1:9">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>211</v>
       </c>
@@ -4411,7 +4416,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="185" spans="1:9">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>212</v>
       </c>
@@ -4428,7 +4433,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="186" spans="1:9">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>213</v>
       </c>
@@ -4445,7 +4450,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="187" spans="1:9">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>214</v>
       </c>
@@ -4459,7 +4464,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="188" spans="1:9">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>215</v>
       </c>
@@ -4482,7 +4487,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="189" spans="1:9">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>217</v>
       </c>
@@ -4499,7 +4504,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="190" spans="1:9">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>218</v>
       </c>
@@ -4516,7 +4521,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="191" spans="1:9">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>219</v>
       </c>
@@ -4530,7 +4535,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="192" spans="1:9">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>220</v>
       </c>
@@ -4547,7 +4552,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="193" spans="1:9">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>221</v>
       </c>
@@ -4561,7 +4566,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="194" spans="1:9">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>222</v>
       </c>
@@ -4575,7 +4580,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="195" spans="1:9">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>223</v>
       </c>
@@ -4589,7 +4594,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="196" spans="1:9">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>224</v>
       </c>
@@ -4603,7 +4608,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="197" spans="1:9">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>225</v>
       </c>
@@ -4617,7 +4622,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="198" spans="1:9">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>226</v>
       </c>
@@ -4634,7 +4639,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="199" spans="1:9">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>227</v>
       </c>
@@ -4651,7 +4656,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="200" spans="1:9">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>228</v>
       </c>
@@ -4668,7 +4673,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="201" spans="1:9">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>229</v>
       </c>
@@ -4688,7 +4693,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="202" spans="1:9">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>231</v>
       </c>
@@ -4702,7 +4707,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="203" spans="1:9">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>232</v>
       </c>
@@ -4725,7 +4730,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="204" spans="1:9">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>234</v>
       </c>
@@ -4742,7 +4747,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="205" spans="1:9">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>235</v>
       </c>
@@ -4759,7 +4764,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="206" spans="1:9">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>236</v>
       </c>
@@ -4776,7 +4781,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="207" spans="1:9">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>237</v>
       </c>
@@ -4796,7 +4801,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="208" spans="1:9">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>240</v>
       </c>
@@ -4813,7 +4818,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="209" spans="1:8">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>241</v>
       </c>
@@ -4824,7 +4829,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="210" spans="1:8">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>242</v>
       </c>
@@ -4841,7 +4846,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="211" spans="1:8">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>243</v>
       </c>
@@ -4858,7 +4863,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="212" spans="1:8">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>244</v>
       </c>
@@ -4875,7 +4880,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="213" spans="1:8">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>245</v>
       </c>
@@ -4889,7 +4894,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="214" spans="1:8">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>246</v>
       </c>
@@ -4903,7 +4908,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="215" spans="1:8">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>247</v>
       </c>
@@ -4917,7 +4922,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="216" spans="1:8">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>248</v>
       </c>
@@ -4934,7 +4939,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="217" spans="1:8">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>249</v>
       </c>
@@ -4954,7 +4959,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="218" spans="1:8">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>250</v>
       </c>
@@ -4968,7 +4973,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>251</v>
       </c>
@@ -4985,7 +4990,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="220" spans="1:8">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>252</v>
       </c>
@@ -5002,7 +5007,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="221" spans="1:8">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>253</v>
       </c>
@@ -5013,7 +5018,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="222" spans="1:8">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>254</v>
       </c>
@@ -5030,7 +5035,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="223" spans="1:8">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>255</v>
       </c>
@@ -5047,7 +5052,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="224" spans="1:8">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>256</v>
       </c>
@@ -5064,7 +5069,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="225" spans="1:9">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>257</v>
       </c>
@@ -5081,7 +5086,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="226" spans="1:9">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>258</v>
       </c>
@@ -5098,7 +5103,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="227" spans="1:9">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>259</v>
       </c>
@@ -5115,7 +5120,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="228" spans="1:9">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>260</v>
       </c>
@@ -5129,7 +5134,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="229" spans="1:9">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>261</v>
       </c>
@@ -5146,7 +5151,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="230" spans="1:9">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>262</v>
       </c>
@@ -5169,7 +5174,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="231" spans="1:9">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>263</v>
       </c>
@@ -5186,7 +5191,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="232" spans="1:9">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>264</v>
       </c>
@@ -5203,7 +5208,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="233" spans="1:9">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>265</v>
       </c>
@@ -5217,7 +5222,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="234" spans="1:9">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>266</v>
       </c>
@@ -5231,7 +5236,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="235" spans="1:9">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>267</v>
       </c>
@@ -5245,7 +5250,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="236" spans="1:9">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>268</v>
       </c>
@@ -5256,7 +5261,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="237" spans="1:9">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>269</v>
       </c>
@@ -5270,7 +5275,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="238" spans="1:9">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>270</v>
       </c>
@@ -5293,7 +5298,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="239" spans="1:9">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>272</v>
       </c>
@@ -5313,7 +5318,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="240" spans="1:9">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>273</v>
       </c>
@@ -5330,7 +5335,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="241" spans="1:9">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>274</v>
       </c>
@@ -5353,7 +5358,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="242" spans="1:9">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>275</v>
       </c>
@@ -5370,7 +5375,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="243" spans="1:9">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>276</v>
       </c>
@@ -5387,7 +5392,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="244" spans="1:9">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>277</v>
       </c>
@@ -5398,7 +5403,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="245" spans="1:9">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>278</v>
       </c>
@@ -5409,7 +5414,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="246" spans="1:9">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>279</v>
       </c>
@@ -5426,7 +5431,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="247" spans="1:9">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>280</v>
       </c>
@@ -5443,7 +5448,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="248" spans="1:9">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>281</v>
       </c>
@@ -5454,7 +5459,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="249" spans="1:9">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>282</v>
       </c>
@@ -5468,7 +5473,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="250" spans="1:9">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>283</v>
       </c>
@@ -5485,7 +5490,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="251" spans="1:9">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>284</v>
       </c>
@@ -5502,7 +5507,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="252" spans="1:9">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>285</v>
       </c>
@@ -5519,7 +5524,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="253" spans="1:9">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>286</v>
       </c>
@@ -5536,7 +5541,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="254" spans="1:9">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>287</v>
       </c>
@@ -5556,7 +5561,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="255" spans="1:9">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>288</v>
       </c>
@@ -5573,7 +5578,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="256" spans="1:9">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>289</v>
       </c>
@@ -5590,7 +5595,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="257" spans="1:9">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>290</v>
       </c>
@@ -5610,7 +5615,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="258" spans="1:9">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>291</v>
       </c>
@@ -5627,7 +5632,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="259" spans="1:9">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>292</v>
       </c>
@@ -5644,7 +5649,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="260" spans="1:9">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>293</v>
       </c>
@@ -5658,7 +5663,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="261" spans="1:9">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>294</v>
       </c>
@@ -5675,7 +5680,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="262" spans="1:9">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>295</v>
       </c>
@@ -5692,7 +5697,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="263" spans="1:9">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>296</v>
       </c>
@@ -5709,7 +5714,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="264" spans="1:9">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>297</v>
       </c>
@@ -5732,7 +5737,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="265" spans="1:9">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>299</v>
       </c>
@@ -5749,7 +5754,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="266" spans="1:9">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>300</v>
       </c>
@@ -5766,7 +5771,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="267" spans="1:9">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>301</v>
       </c>
@@ -5783,7 +5788,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="268" spans="1:9">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>302</v>
       </c>
@@ -5800,7 +5805,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="269" spans="1:9">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>303</v>
       </c>
@@ -5820,7 +5825,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="270" spans="1:9">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>304</v>
       </c>
@@ -5834,7 +5839,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="271" spans="1:9">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>305</v>
       </c>
@@ -5851,7 +5856,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="272" spans="1:9">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>306</v>
       </c>
@@ -5862,7 +5867,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="273" spans="1:9">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>307</v>
       </c>
@@ -5879,7 +5884,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="274" spans="1:9">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>308</v>
       </c>
@@ -5896,7 +5901,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="275" spans="1:9">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>309</v>
       </c>
@@ -5913,7 +5918,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="276" spans="1:9">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>310</v>
       </c>
@@ -5930,7 +5935,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="277" spans="1:9">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>311</v>
       </c>
@@ -5947,7 +5952,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="278" spans="1:9">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>312</v>
       </c>
@@ -5964,7 +5969,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="279" spans="1:9">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>313</v>
       </c>
@@ -5981,7 +5986,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="280" spans="1:9">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>314</v>
       </c>
@@ -5995,7 +6000,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="281" spans="1:9">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>315</v>
       </c>
@@ -6006,7 +6011,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="282" spans="1:9">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>316</v>
       </c>
@@ -6023,7 +6028,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="283" spans="1:9">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>317</v>
       </c>
@@ -6037,7 +6042,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="284" spans="1:9">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>318</v>
       </c>
@@ -6054,7 +6059,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="285" spans="1:9">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>319</v>
       </c>
@@ -6074,7 +6079,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="286" spans="1:9">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>320</v>
       </c>
@@ -6094,7 +6099,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="287" spans="1:9">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>321</v>
       </c>
@@ -6114,7 +6119,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="288" spans="1:9">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>322</v>
       </c>
@@ -6134,7 +6139,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="289" spans="1:9">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>324</v>
       </c>
@@ -6145,7 +6150,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="290" spans="1:9">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>325</v>
       </c>
@@ -6156,7 +6161,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="291" spans="1:9">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>326</v>
       </c>
@@ -6167,7 +6172,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="292" spans="1:9">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>327</v>
       </c>
@@ -6190,7 +6195,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="293" spans="1:9">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>330</v>
       </c>
@@ -6213,7 +6218,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="294" spans="1:9">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>331</v>
       </c>
@@ -6224,7 +6229,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="295" spans="1:9">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>332</v>
       </c>
@@ -6235,7 +6240,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="296" spans="1:9">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>333</v>
       </c>
@@ -6246,7 +6251,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="297" spans="1:9">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>334</v>
       </c>
@@ -6266,7 +6271,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="298" spans="1:9">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>335</v>
       </c>
@@ -6286,7 +6291,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="299" spans="1:9">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>336</v>
       </c>
@@ -6297,7 +6302,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="300" spans="1:9">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>337</v>
       </c>
@@ -6314,7 +6319,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="301" spans="1:9">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>338</v>
       </c>
@@ -6337,7 +6342,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="302" spans="1:9">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>340</v>
       </c>
@@ -6354,7 +6359,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="303" spans="1:9">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>341</v>
       </c>
@@ -6371,7 +6376,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="304" spans="1:9">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>342</v>
       </c>
@@ -6388,7 +6393,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="305" spans="1:9">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>343</v>
       </c>
@@ -6402,7 +6407,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="306" spans="1:9">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>344</v>
       </c>
@@ -6413,7 +6418,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="307" spans="1:9">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>345</v>
       </c>
@@ -6430,7 +6435,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="308" spans="1:9">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>346</v>
       </c>
@@ -6447,7 +6452,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="309" spans="1:9">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>347</v>
       </c>
@@ -6458,7 +6463,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="310" spans="1:9">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>348</v>
       </c>
@@ -6481,7 +6486,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="311" spans="1:9">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>350</v>
       </c>
@@ -6498,7 +6503,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="312" spans="1:9">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>351</v>
       </c>
@@ -6515,7 +6520,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="313" spans="1:9">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>352</v>
       </c>
@@ -6526,7 +6531,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="314" spans="1:9">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>353</v>
       </c>
@@ -6543,7 +6548,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="315" spans="1:9">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>354</v>
       </c>
@@ -6563,7 +6568,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="316" spans="1:9">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>356</v>
       </c>
@@ -6583,7 +6588,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="317" spans="1:9">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>358</v>
       </c>
@@ -6603,7 +6608,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="318" spans="1:9">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>359</v>
       </c>
@@ -6620,7 +6625,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="319" spans="1:9">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>360</v>
       </c>
@@ -6634,7 +6639,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="320" spans="1:9">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>361</v>
       </c>
@@ -6645,7 +6650,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="321" spans="1:9">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>362</v>
       </c>
@@ -6656,7 +6661,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="322" spans="1:9">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>363</v>
       </c>
@@ -6667,7 +6672,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="323" spans="1:9">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>364</v>
       </c>
@@ -6681,7 +6686,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="324" spans="1:9">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>365</v>
       </c>
@@ -6695,7 +6700,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="325" spans="1:9">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>366</v>
       </c>
@@ -6712,7 +6717,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="326" spans="1:9">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>367</v>
       </c>
@@ -6729,7 +6734,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="327" spans="1:9">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>368</v>
       </c>
@@ -6746,7 +6751,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="328" spans="1:9">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>369</v>
       </c>
@@ -6763,7 +6768,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="329" spans="1:9">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>370</v>
       </c>
@@ -6783,7 +6788,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="330" spans="1:9">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>371</v>
       </c>
@@ -6800,7 +6805,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="331" spans="1:9">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>372</v>
       </c>
@@ -6817,7 +6822,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="332" spans="1:9">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>373</v>
       </c>
@@ -6837,7 +6842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:9">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>374</v>
       </c>
@@ -6857,7 +6862,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="334" spans="1:9">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>375</v>
       </c>
@@ -6880,7 +6885,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="335" spans="1:9">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>377</v>
       </c>
@@ -6897,7 +6902,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="336" spans="1:9">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>378</v>
       </c>
@@ -6914,7 +6919,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="337" spans="1:8">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>379</v>
       </c>
@@ -6931,7 +6936,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="338" spans="1:8">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>380</v>
       </c>
@@ -6942,7 +6947,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="339" spans="1:8">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>381</v>
       </c>
@@ -6959,7 +6964,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="340" spans="1:8">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>382</v>
       </c>
@@ -6973,7 +6978,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="341" spans="1:8">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>383</v>
       </c>
@@ -6993,7 +6998,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="342" spans="1:8">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>384</v>
       </c>
@@ -7010,7 +7015,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="343" spans="1:8">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>385</v>
       </c>
@@ -7024,7 +7029,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="344" spans="1:8">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>386</v>
       </c>
@@ -7038,7 +7043,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="345" spans="1:8">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>387</v>
       </c>
@@ -7049,7 +7054,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="346" spans="1:8">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>388</v>
       </c>
@@ -7060,7 +7065,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="347" spans="1:8">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>389</v>
       </c>
@@ -7074,7 +7079,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="348" spans="1:8">
+    <row r="348" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>390</v>
       </c>
@@ -7091,7 +7096,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="349" spans="1:8">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>391</v>
       </c>
@@ -7111,7 +7116,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="350" spans="1:8">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>392</v>
       </c>
@@ -7131,7 +7136,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="351" spans="1:8">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>393</v>
       </c>
@@ -7151,7 +7156,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="352" spans="1:8">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>394</v>
       </c>
@@ -7168,7 +7173,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="353" spans="1:9">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>395</v>
       </c>
@@ -7182,7 +7187,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="354" spans="1:9">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>396</v>
       </c>
@@ -7199,7 +7204,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="355" spans="1:9">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>397</v>
       </c>
@@ -7210,7 +7215,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="356" spans="1:9">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>398</v>
       </c>
@@ -7227,7 +7232,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="357" spans="1:9">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>399</v>
       </c>
@@ -7238,7 +7243,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="358" spans="1:9">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>400</v>
       </c>
@@ -7255,7 +7260,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="359" spans="1:9">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>401</v>
       </c>
@@ -7275,7 +7280,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="360" spans="1:9">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>402</v>
       </c>
@@ -7292,7 +7297,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="361" spans="1:9">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>403</v>
       </c>
@@ -7312,7 +7317,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="362" spans="1:9">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>404</v>
       </c>
@@ -7332,7 +7337,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="363" spans="1:9">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>405</v>
       </c>
@@ -7350,7 +7355,7 @@
       </c>
       <c r="I363" s="1"/>
     </row>
-    <row r="364" spans="1:9">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>406</v>
       </c>
@@ -7370,7 +7375,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="365" spans="1:9">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>407</v>
       </c>
@@ -7384,7 +7389,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="366" spans="1:9">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>408</v>
       </c>
@@ -7395,7 +7400,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="367" spans="1:9">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>409</v>
       </c>
@@ -7412,7 +7417,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="368" spans="1:9">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>410</v>
       </c>
@@ -7429,7 +7434,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="369" spans="1:9">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>411</v>
       </c>
@@ -7446,7 +7451,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="370" spans="1:9">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>412</v>
       </c>
@@ -7466,7 +7471,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="371" spans="1:9">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>413</v>
       </c>
@@ -7483,7 +7488,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="372" spans="1:9">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>414</v>
       </c>
@@ -7506,7 +7511,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="373" spans="1:9">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>415</v>
       </c>
@@ -7520,7 +7525,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="374" spans="1:9">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>416</v>
       </c>
@@ -7531,7 +7536,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="375" spans="1:9">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>417</v>
       </c>
@@ -7542,7 +7547,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="376" spans="1:9">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>418</v>
       </c>
@@ -7553,7 +7558,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="377" spans="1:9">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>419</v>
       </c>
@@ -7567,7 +7572,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="378" spans="1:9">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>420</v>
       </c>
@@ -7581,9 +7586,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="379" spans="1:9">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>421</v>
+        <v>456</v>
       </c>
       <c r="B379" t="s">
         <v>25</v>
@@ -7598,9 +7603,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="380" spans="1:9">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B380" t="s">
         <v>25</v>
@@ -7615,20 +7620,20 @@
         <v>33</v>
       </c>
     </row>
-    <row r="381" spans="1:9">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
+        <v>422</v>
+      </c>
+      <c r="B381" t="s">
+        <v>10</v>
+      </c>
+      <c r="C381" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A382" t="s">
         <v>423</v>
-      </c>
-      <c r="B381" t="s">
-        <v>10</v>
-      </c>
-      <c r="C381" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="382" spans="1:9">
-      <c r="A382" t="s">
-        <v>424</v>
       </c>
       <c r="B382" t="s">
         <v>25</v>
@@ -7643,23 +7648,23 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="383" spans="1:9">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
+        <v>424</v>
+      </c>
+      <c r="B383" t="s">
+        <v>25</v>
+      </c>
+      <c r="C383" t="s">
+        <v>25</v>
+      </c>
+      <c r="D383" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A384" t="s">
         <v>425</v>
-      </c>
-      <c r="B383" t="s">
-        <v>25</v>
-      </c>
-      <c r="C383" t="s">
-        <v>25</v>
-      </c>
-      <c r="D383" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="384" spans="1:9">
-      <c r="A384" t="s">
-        <v>426</v>
       </c>
       <c r="B384" t="s">
         <v>10</v>
@@ -7671,112 +7676,112 @@
         <v>109</v>
       </c>
     </row>
-    <row r="385" spans="1:5">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
+        <v>426</v>
+      </c>
+      <c r="B385" t="s">
+        <v>10</v>
+      </c>
+      <c r="C385" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A386" t="s">
         <v>427</v>
       </c>
-      <c r="B385" t="s">
-        <v>10</v>
-      </c>
-      <c r="C385" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="386" spans="1:5">
-      <c r="A386" t="s">
+      <c r="B386" t="s">
+        <v>10</v>
+      </c>
+      <c r="C386" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A387" t="s">
         <v>428</v>
       </c>
-      <c r="B386" t="s">
-        <v>10</v>
-      </c>
-      <c r="C386" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="387" spans="1:5">
-      <c r="A387" t="s">
+      <c r="B387" t="s">
+        <v>10</v>
+      </c>
+      <c r="C387" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A388" t="s">
         <v>429</v>
       </c>
-      <c r="B387" t="s">
-        <v>10</v>
-      </c>
-      <c r="C387" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="388" spans="1:5">
-      <c r="A388" t="s">
+      <c r="B388" t="s">
+        <v>25</v>
+      </c>
+      <c r="C388" t="s">
+        <v>25</v>
+      </c>
+      <c r="D388" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A389" t="s">
         <v>430</v>
       </c>
-      <c r="B388" t="s">
-        <v>25</v>
-      </c>
-      <c r="C388" t="s">
-        <v>25</v>
-      </c>
-      <c r="D388" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="389" spans="1:5">
-      <c r="A389" t="s">
+      <c r="B389" t="s">
+        <v>25</v>
+      </c>
+      <c r="C389" t="s">
+        <v>25</v>
+      </c>
+      <c r="D389" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A390" t="s">
         <v>431</v>
       </c>
-      <c r="B389" t="s">
-        <v>25</v>
-      </c>
-      <c r="C389" t="s">
-        <v>25</v>
-      </c>
-      <c r="D389" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="390" spans="1:5">
-      <c r="A390" t="s">
+      <c r="B390" t="s">
+        <v>25</v>
+      </c>
+      <c r="C390" t="s">
+        <v>25</v>
+      </c>
+      <c r="D390" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A391" t="s">
         <v>432</v>
       </c>
-      <c r="B390" t="s">
-        <v>25</v>
-      </c>
-      <c r="C390" t="s">
-        <v>25</v>
-      </c>
-      <c r="D390" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="391" spans="1:5">
-      <c r="A391" t="s">
+      <c r="B391" t="s">
+        <v>25</v>
+      </c>
+      <c r="C391" t="s">
+        <v>10</v>
+      </c>
+      <c r="D391" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A392" t="s">
         <v>433</v>
       </c>
-      <c r="B391" t="s">
-        <v>25</v>
-      </c>
-      <c r="C391" t="s">
-        <v>10</v>
-      </c>
-      <c r="D391" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="392" spans="1:5">
-      <c r="A392" t="s">
+      <c r="B392" t="s">
+        <v>25</v>
+      </c>
+      <c r="C392" t="s">
+        <v>25</v>
+      </c>
+      <c r="D392" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A393" t="s">
         <v>434</v>
-      </c>
-      <c r="B392" t="s">
-        <v>25</v>
-      </c>
-      <c r="C392" t="s">
-        <v>25</v>
-      </c>
-      <c r="D392" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="393" spans="1:5">
-      <c r="A393" t="s">
-        <v>435</v>
       </c>
       <c r="B393" t="s">
         <v>10</v>
@@ -7791,9 +7796,9 @@
         <v>109</v>
       </c>
     </row>
-    <row r="394" spans="1:5">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B394" t="s">
         <v>25</v>
@@ -7808,9 +7813,9 @@
         <v>109</v>
       </c>
     </row>
-    <row r="395" spans="1:5">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B395" t="s">
         <v>10</v>
@@ -7825,9 +7830,9 @@
         <v>109</v>
       </c>
     </row>
-    <row r="396" spans="1:5">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B396" t="s">
         <v>25</v>
@@ -7842,9 +7847,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="397" spans="1:5">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B397" t="s">
         <v>25</v>
@@ -7859,9 +7864,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="398" spans="1:5">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B398" t="s">
         <v>10</v>
@@ -7876,9 +7881,9 @@
         <v>109</v>
       </c>
     </row>
-    <row r="399" spans="1:5">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B399" t="s">
         <v>10</v>
@@ -7893,23 +7898,23 @@
         <v>109</v>
       </c>
     </row>
-    <row r="400" spans="1:5">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
+        <v>441</v>
+      </c>
+      <c r="B400" t="s">
+        <v>25</v>
+      </c>
+      <c r="C400" t="s">
+        <v>25</v>
+      </c>
+      <c r="D400" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A401" t="s">
         <v>442</v>
-      </c>
-      <c r="B400" t="s">
-        <v>25</v>
-      </c>
-      <c r="C400" t="s">
-        <v>25</v>
-      </c>
-      <c r="D400" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="401" spans="1:8">
-      <c r="A401" t="s">
-        <v>443</v>
       </c>
       <c r="B401" t="s">
         <v>10</v>
@@ -7924,9 +7929,9 @@
         <v>109</v>
       </c>
     </row>
-    <row r="402" spans="1:8">
+    <row r="402" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B402" t="s">
         <v>10</v>
@@ -7941,9 +7946,9 @@
         <v>109</v>
       </c>
     </row>
-    <row r="403" spans="1:8">
+    <row r="403" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B403" t="s">
         <v>25</v>
@@ -7958,9 +7963,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="404" spans="1:8">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B404" t="s">
         <v>10</v>
@@ -7975,23 +7980,23 @@
         <v>109</v>
       </c>
     </row>
-    <row r="405" spans="1:8">
+    <row r="405" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
+        <v>446</v>
+      </c>
+      <c r="B405" t="s">
+        <v>25</v>
+      </c>
+      <c r="C405" t="s">
+        <v>25</v>
+      </c>
+      <c r="D405" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A406" t="s">
         <v>447</v>
-      </c>
-      <c r="B405" t="s">
-        <v>25</v>
-      </c>
-      <c r="C405" t="s">
-        <v>25</v>
-      </c>
-      <c r="D405" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="406" spans="1:8">
-      <c r="A406" t="s">
-        <v>448</v>
       </c>
       <c r="B406" t="s">
         <v>10</v>
@@ -8006,9 +8011,9 @@
         <v>109</v>
       </c>
     </row>
-    <row r="407" spans="1:8">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B407" t="s">
         <v>25</v>
@@ -8023,9 +8028,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="408" spans="1:8">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B408" t="s">
         <v>24</v>
@@ -8043,23 +8048,23 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="409" spans="1:8">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
+        <v>450</v>
+      </c>
+      <c r="B409" t="s">
+        <v>25</v>
+      </c>
+      <c r="C409" t="s">
+        <v>25</v>
+      </c>
+      <c r="D409" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A410" t="s">
         <v>451</v>
-      </c>
-      <c r="B409" t="s">
-        <v>25</v>
-      </c>
-      <c r="C409" t="s">
-        <v>25</v>
-      </c>
-      <c r="D409" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="410" spans="1:8">
-      <c r="A410" t="s">
-        <v>452</v>
       </c>
       <c r="B410" t="s">
         <v>24</v>
@@ -8074,23 +8079,23 @@
         <v>117</v>
       </c>
       <c r="H410" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A411" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="411" spans="1:8">
-      <c r="A411" t="s">
+      <c r="B411" t="s">
+        <v>10</v>
+      </c>
+      <c r="C411" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A412" t="s">
         <v>454</v>
-      </c>
-      <c r="B411" t="s">
-        <v>10</v>
-      </c>
-      <c r="C411" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="412" spans="1:8">
-      <c r="A412" t="s">
-        <v>455</v>
       </c>
       <c r="B412" t="s">
         <v>25</v>
@@ -8105,12 +8110,12 @@
         <v>23</v>
       </c>
       <c r="H412" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="413" spans="1:8">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B413" t="s">
         <v>25</v>
@@ -8126,14 +8131,14 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D413 B1:C1048576">
+  <conditionalFormatting sqref="B1:C1048576 D2:D413">
     <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E413">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
-      <formula>"doublet drops"</formula>
+  <conditionalFormatting sqref="B1:C1048576">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E413">
@@ -8145,10 +8150,8 @@
     <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"doublet"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:C1048576">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>"yes"</formula>
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+      <formula>"doublet drops"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
